--- a/modele_actes.xlsx
+++ b/modele_actes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marou\WebstormProjects\medical-office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9173F6-C751-46C8-8D07-6185107ADAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDB6015-7F7A-412A-A918-BA96AC713350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,25 +20,382 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Libelle</t>
-  </si>
-  <si>
-    <t>Prix</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>DDD</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
+  <si>
+    <t>Consultations &amp; Radio</t>
+  </si>
+  <si>
+    <t>DCH000010</t>
+  </si>
+  <si>
+    <t>Consultation au cabinet du médecin dentiste</t>
+  </si>
+  <si>
+    <t>Anesthésie locale isolée (sans acte associé)</t>
+  </si>
+  <si>
+    <t>DCH000020</t>
+  </si>
+  <si>
+    <t>Anesthésie locorégionale</t>
+  </si>
+  <si>
+    <t>DCH000030</t>
+  </si>
+  <si>
+    <t>Radiographie intrabuccale (rétro-alvéolaire / occlusale)</t>
+  </si>
+  <si>
+    <t>DCH000040</t>
+  </si>
+  <si>
+    <t>Status radiologique complet intrabuccal</t>
+  </si>
+  <si>
+    <t>Hors-Nomenclature</t>
+  </si>
+  <si>
+    <t>Lecture Radiographie panoramique dentaire</t>
+  </si>
+  <si>
+    <t>Lecture CONE BEAM dentaire</t>
+  </si>
+  <si>
+    <t>Etablissement d'un plan de traitement complexe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sondage/ Charting Parodontal </t>
+  </si>
+  <si>
+    <t>Empreinte Numèrique</t>
+  </si>
+  <si>
+    <t>Soins Conservateurs</t>
+  </si>
+  <si>
+    <t>DCH000110</t>
+  </si>
+  <si>
+    <t>Curetage de carie + Obturation une face (Résine Composite)</t>
+  </si>
+  <si>
+    <t>DCH000120</t>
+  </si>
+  <si>
+    <t>Curetage de carie + Obturation deux faces (Résine Composite)</t>
+  </si>
+  <si>
+    <t>DCH000130</t>
+  </si>
+  <si>
+    <t>Curetage de carie + Obturation trois faces et plus (Résine Composite) avec ou sans renforcement en Ribbond</t>
+  </si>
+  <si>
+    <t>DCH000140</t>
+  </si>
+  <si>
+    <t>Restauration coronaire avec ancrage radiculaire (Résine composite avec un tenon fibré)</t>
+  </si>
+  <si>
+    <t>DCH000150</t>
+  </si>
+  <si>
+    <t>Pulpotomie (sur dent temporaire ou permanente) acte d'urgence en dehors du traitement endodontique final</t>
+  </si>
+  <si>
+    <t>Application de vernis fluoré ou scellement de sillons</t>
+  </si>
+  <si>
+    <t>Endodontie</t>
+  </si>
+  <si>
+    <t>DCH000210</t>
+  </si>
+  <si>
+    <t>Traitement endodontique (Dévitalisation) mono-radiculée</t>
+  </si>
+  <si>
+    <t>DCH000220</t>
+  </si>
+  <si>
+    <t>Traitement endodontique (Dévitalisation) bi-radiculée</t>
+  </si>
+  <si>
+    <t>DCH000230</t>
+  </si>
+  <si>
+    <t>Traitement endodontique (Dévitalisation) pluri-radiculée</t>
+  </si>
+  <si>
+    <t>DCH000240</t>
+  </si>
+  <si>
+    <t>Traitement d'un canal calcifié ou reprise de traitement</t>
+  </si>
+  <si>
+    <t>Prophylaxie &amp; Paro</t>
+  </si>
+  <si>
+    <t>DCH030010</t>
+  </si>
+  <si>
+    <t>Détartrage complet (sus et sous-gingival) MAXILLAIRE (supérieur)</t>
+  </si>
+  <si>
+    <t>Détartrage complet (sus et sous-gingival) MANDIBULAIRE  (inférieur)</t>
+  </si>
+  <si>
+    <t>Détartrage complet (sus et sous-gingival) MAXILLAIRE (supérieur) + Aéropolissage (Airflow Ems)</t>
+  </si>
+  <si>
+    <t>Détartrage complet (sus et sous-gingival) MANDIBULAIRE  (inférieur) +Aéropolissage (Airflow Ems)</t>
+  </si>
+  <si>
+    <t>DCH030020</t>
+  </si>
+  <si>
+    <t>Traitement des parodontopathies - Détartrage Surfaçage radiculaire + Curetage parodontal - Sextant Maxillaire droit</t>
+  </si>
+  <si>
+    <t>Traitement des parodontopathies - Détartrage Surfaçage radiculaire + Curetage parodontal - Sextant Maxillaire Gauche</t>
+  </si>
+  <si>
+    <t>Traitement des parodontopathies - Détartrage Surfaçage radiculaire + Curetage parodontal - Sextant Mandibulaire Droit</t>
+  </si>
+  <si>
+    <t>Traitement des parodontopathies - Détartrage Surfaçage radiculaire + Curetage parodontal - Sextant Mandibulaire Gauche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance - Détartrage Supra/sous gingival - Aéropolissage au niveau de toute la cavité orale </t>
+  </si>
+  <si>
+    <t>DCH030080</t>
+  </si>
+  <si>
+    <t>Greffe Epithèlioconjonctive associèe ou non à une Frénéctomie labiale avec prélévement et Sutures</t>
+  </si>
+  <si>
+    <t>DCH030030</t>
+  </si>
+  <si>
+    <t>Gingivectomie Partielle (une seule dent) quelque soit la technique</t>
+  </si>
+  <si>
+    <t>DCH030040</t>
+  </si>
+  <si>
+    <t>Gingivectomie étendue à une hémiarcade ou de canine à canine quelque soit la technique</t>
+  </si>
+  <si>
+    <t>DCH030050</t>
+  </si>
+  <si>
+    <t>Lambeau d'exploration/assainissement entre une à 03 dents</t>
+  </si>
+  <si>
+    <t>DCH030060</t>
+  </si>
+  <si>
+    <t>Lambeau d'exploration/assainissement supplémentaire par dent</t>
+  </si>
+  <si>
+    <t>DCH030070</t>
+  </si>
+  <si>
+    <t>Lambeau d'exploration/assainissement associèe à une technique de comblement quelque soit le produit utilisé + Sutures</t>
+  </si>
+  <si>
+    <t>DCH030100</t>
+  </si>
+  <si>
+    <t>Contention Métallique - de canine à canine - Parodontopathie</t>
+  </si>
+  <si>
+    <t>Contention Métallique - de canine à canine - Reliance - Parodontopathie</t>
+  </si>
+  <si>
+    <t>Contention en Fibre de Verre - Ribbond - de canine à canine - Reliance - Parodontopathie</t>
+  </si>
+  <si>
+    <t>DCH030130</t>
+  </si>
+  <si>
+    <t>Modification de l'articulé par Meulage Sélectif</t>
+  </si>
+  <si>
+    <t>Chirurgie Buccale</t>
+  </si>
+  <si>
+    <t>DCH000420</t>
+  </si>
+  <si>
+    <t>Extraction d'une dent temporaire</t>
+  </si>
+  <si>
+    <t>DCH000410</t>
+  </si>
+  <si>
+    <t>Extraction d'une dent permanente (sans alvéoléctomie)</t>
+  </si>
+  <si>
+    <t>Extraction d'une dent permanente avec lambeau, séparation radiculaire avec éponge de collagène + Sutures</t>
+  </si>
+  <si>
+    <t>Extraction de dent de sagesse sur arcade, sans lambeau avec éponge de collagène + Sutures</t>
+  </si>
+  <si>
+    <t>DCH000430</t>
+  </si>
+  <si>
+    <t>Extraction de dent de sagesse enclavée, avec lambeau, Ostéotomie, séparation coronaire et/ou radiculaire, éponge de collagène et Sutures</t>
+  </si>
+  <si>
+    <t>Extraction de dent de sagesse incluse, avec lambeau, Ostéotomie, séparation coronaire et/ou radiculaire, éponge de collagène et Sutures</t>
+  </si>
+  <si>
+    <t>DCH000440</t>
+  </si>
+  <si>
+    <t>Alvéoléctomie ou régularisation de la crête alvéolaire</t>
+  </si>
+  <si>
+    <t>DCH000450</t>
+  </si>
+  <si>
+    <t>Frénectomie (labiale ou linguale)</t>
+  </si>
+  <si>
+    <t>DCH000460</t>
+  </si>
+  <si>
+    <t>Incision d'abcès d'origine dentaire</t>
+  </si>
+  <si>
+    <t>DCH000470</t>
+  </si>
+  <si>
+    <t>Résection apicale avec obturation a retro</t>
+  </si>
+  <si>
+    <t>Prothèse Dentaire</t>
+  </si>
+  <si>
+    <t>DCH060200</t>
+  </si>
+  <si>
+    <t>Couronne dentaire Zircone (par dent)</t>
+  </si>
+  <si>
+    <t>Couronne dentaire Zircone Multilayer (par dent)</t>
+  </si>
+  <si>
+    <t>Couronne dentaire Zircone  (par unité de bridge)</t>
+  </si>
+  <si>
+    <t>Couronne dentaire Zircone Multilayer  (par unité de bridge)</t>
+  </si>
+  <si>
+    <t>Couronne dentaire Céramo- Zircone Multilayer (par dent)</t>
+  </si>
+  <si>
+    <t>Facette en Céramique pressée</t>
+  </si>
+  <si>
+    <t>DCH060210</t>
+  </si>
+  <si>
+    <t>Reconstitution corono-radiculaire foulée (fibrée)</t>
+  </si>
+  <si>
+    <t>DCH060220</t>
+  </si>
+  <si>
+    <t>Reconstitution corono-radiculaire coulée</t>
+  </si>
+  <si>
+    <t>DCH060240</t>
+  </si>
+  <si>
+    <t>Dépose et repose de prothèse fixe (par unité)</t>
+  </si>
+  <si>
+    <t>DCH060060</t>
+  </si>
+  <si>
+    <t>Appareil amovible complet ( Résine Flexit)</t>
+  </si>
+  <si>
+    <t>DCH060010</t>
+  </si>
+  <si>
+    <t>Appareil amovible de 01 à 04 dents ( Résine Flexit)</t>
+  </si>
+  <si>
+    <t>DCH060030</t>
+  </si>
+  <si>
+    <t>Appareil amovible de 05 à 08 dents ( Résine Flexit)</t>
+  </si>
+  <si>
+    <t>DCH060050</t>
+  </si>
+  <si>
+    <t>Appareil amovible entre 10 à 14 dents ( Résine Flexit)</t>
+  </si>
+  <si>
+    <t>Implantologie</t>
+  </si>
+  <si>
+    <t>DCH090010</t>
+  </si>
+  <si>
+    <t>Mise en place d'un implant Straumann Titane</t>
+  </si>
+  <si>
+    <t>Mise en place d'un implant Straumann Roxolid</t>
+  </si>
+  <si>
+    <t>Mise en place d'un implant Neodont</t>
+  </si>
+  <si>
+    <t>DCH090030</t>
+  </si>
+  <si>
+    <t>Mise en place d'une couronne Zircone Multi-layer sur implant Straumann (Titane ou Roxolid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place d'une couronne Zircone Multi-layer sur implant Neodent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greffe d'apposition (Régénération osseuse Guidée) associée à la mise en place d'implant </t>
+  </si>
+  <si>
+    <t>Sinus Lift par voie Verticale, associée ou non à la mise en place d'implant</t>
+  </si>
+  <si>
+    <t>Sinus Lift par voie Latérale, associée ou non à la mise en place d'implant</t>
+  </si>
+  <si>
+    <t>Préservation alvéolaire (en dehors de l'extraction dentaire)</t>
+  </si>
+  <si>
+    <t>Famille</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Tarif</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,18 +406,116 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EAE9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E399"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7533"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6BA98"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,13 +523,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF363840"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,33 +910,1020 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="D2" s="4">
+        <v>60</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="D3" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4">
         <v>100</v>
       </c>
-      <c r="C2">
-        <v>123</v>
+    </row>
+    <row r="7" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="9">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="9">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="140.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="154.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="154.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="154.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="12">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="98.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="12">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="140.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="12">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="98.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="12">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="12">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" s="18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="18">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="18">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="182.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="18">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="182.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="18">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="18">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="18">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="18">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="21">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="21">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="21">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="21">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="21">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="21">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D60" s="21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="21">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="21">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="21">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="24">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" s="24">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="24">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="24">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="98.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" s="24">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="112.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D69" s="24">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="24">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" s="24">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D72" s="24">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
